--- a/Assignments/HW3/Shoe Comfort Experiment.xlsx
+++ b/Assignments/HW3/Shoe Comfort Experiment.xlsx
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>6.373546189257667</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>7.183643324222082</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>6.164371387589953</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>7.595280802137792</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>6.329507771815361</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="7">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>5.179531615881984</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="8">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>8.287429052428486</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>8.538324705129217</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>8.375781351653492</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>6.194611612843644</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="12">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>8.011781168450849</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>6.889843236411431</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>8.478759419458196</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="15">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>6.8853001128225</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="16">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>10.22493091814311</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="17">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>7.955066390984769</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>7.983809736901054</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>8.9438362106853</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="20">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D20">
-        <v>11.07122119509809</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="21">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>10.84390132121751</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="22">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>11.16897737160822</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="23">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>9.482136300731067</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="24">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>8.77456498336519</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>6.710648304136626</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
